--- a/assets-source/map/map-def.xlsx
+++ b/assets-source/map/map-def.xlsx
@@ -5,25 +5,71 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/john/Projects/60_soho/30_Personal/GameCreator/godot-crystal-tales/temp_assets/map/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/john/Projects/60_soho/30_Personal/GameCreator/godot-crystal-tales/assets-source/map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB241FF-0D4C-EC4E-B439-10EE4F721EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9ACB7A-3CDC-C645-BCE9-0DDA62DB1336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15020" yWindow="-23480" windowWidth="27700" windowHeight="17400" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31600" yWindow="-3940" windowWidth="27700" windowHeight="17400" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="地圖一覽表" sheetId="1" r:id="rId1"/>
     <sheet name="芳蕾鎮-M1" sheetId="2" r:id="rId2"/>
     <sheet name="北方礦山-M2" sheetId="3" r:id="rId3"/>
     <sheet name="東之森-M3" sheetId="4" r:id="rId4"/>
+    <sheet name="東之森深處-M4" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="41">
+  <si>
+    <t>簡易地圖</t>
+  </si>
+  <si>
+    <t>格</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>ー</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
   <si>
     <t>代號</t>
   </si>
@@ -34,9 +80,6 @@
     <t>檔案前綴</t>
   </si>
   <si>
-    <t>M1</t>
-  </si>
-  <si>
     <t>芳蕾鎮</t>
   </si>
   <si>
@@ -61,64 +104,54 @@
     <t>east-forest</t>
   </si>
   <si>
-    <t>M4</t>
-  </si>
-  <si>
-    <t>新區域</t>
+    <t>東之森深處</t>
+  </si>
+  <si>
+    <t>east-forest-depths</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>通往大都市的路</t>
   </si>
   <si>
     <t>xxxx</t>
   </si>
   <si>
-    <t>M5</t>
-  </si>
-  <si>
-    <t>通往大都市的路</t>
-  </si>
-  <si>
-    <t>簡易地圖</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>g</t>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>n</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>M6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>a</t>
+    <t>新的地圖</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>|</t>
+    <t>xxxx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ー</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>l</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -155,80 +188,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -252,7 +217,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -262,32 +227,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -624,77 +577,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +674,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -721,87 +685,87 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="9" width="3" customWidth="1"/>
+    <col min="2" max="9" width="3" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="B2" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>20</v>
+      <c r="B2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="B3" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="12"/>
+      <c r="B3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="B4" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="12"/>
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="B5" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="B5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="B6" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="B6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -811,86 +775,437 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="7" width="3.85546875" style="11" customWidth="1"/>
+    <col min="2" max="17" width="4" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20" customHeight="1">
+    <row r="1" spans="1:12" ht="20" customHeight="1">
       <c r="A1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
+      <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12">
       <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
+      <c r="C3" s="1"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" ht="19" customHeight="1" thickBot="1">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12">
       <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
+      <c r="C4" s="1"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" ht="20" customHeight="1" thickBot="1">
-      <c r="B5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="G4" s="2"/>
+      <c r="H4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="19" customHeight="1">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" ht="19" customHeight="1" thickBot="1">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="20" customHeight="1" thickBot="1">
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="20" customHeight="1">
+      <c r="B8" s="1"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="7"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4" t="s">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="16" width="3.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="19" thickBot="1"/>
+    <row r="3" spans="1:16" ht="19" thickBot="1">
+      <c r="B3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="B7" s="1"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="1"/>
+      <c r="C3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:16" ht="19" thickBot="1">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:16" ht="19" thickBot="1">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/assets-source/map/map-def.xlsx
+++ b/assets-source/map/map-def.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/john/Projects/60_soho/30_Personal/GameCreator/godot-crystal-tales/assets-source/map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9ACB7A-3CDC-C645-BCE9-0DDA62DB1336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C309C17-622A-A346-AC01-4D8975202C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31600" yWindow="-3940" windowWidth="27700" windowHeight="17400" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1220" yWindow="600" windowWidth="27580" windowHeight="17400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="地圖一覽表" sheetId="1" r:id="rId1"/>
@@ -180,12 +180,18 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -217,7 +223,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -243,6 +249,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -258,6 +267,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>5861</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9768</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>650631</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>83037</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A6E3D4E-5358-E1FC-B2EA-A53E3AE06EED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5535246" y="263768"/>
+          <a:ext cx="5529385" cy="6911731"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -954,7 +1012,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="2"/>
@@ -965,6 +1023,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/assets-source/map/map-def.xlsx
+++ b/assets-source/map/map-def.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/john/Projects/60_soho/30_Personal/GameCreator/godot-crystal-tales/assets-source/map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C309C17-622A-A346-AC01-4D8975202C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9252A9-CB81-8C47-8AC4-0320EC7E0032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="600" windowWidth="27580" windowHeight="17400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1220" yWindow="600" windowWidth="27580" windowHeight="17400" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="地圖一覽表" sheetId="1" r:id="rId1"/>
@@ -267,55 +267,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>5861</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>9768</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>650631</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>83037</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="圖片 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A6E3D4E-5358-E1FC-B2EA-A53E3AE06EED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5535246" y="263768"/>
-          <a:ext cx="5529385" cy="6911731"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1023,7 +974,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/assets-source/map/map-def.xlsx
+++ b/assets-source/map/map-def.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/john/Projects/60_soho/30_Personal/GameCreator/godot-crystal-tales/assets-source/map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9252A9-CB81-8C47-8AC4-0320EC7E0032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3961CD-E45B-7448-9422-EF2CD3ECCB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="600" windowWidth="27580" windowHeight="17400" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="600" windowWidth="24520" windowHeight="15400" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="地圖一覽表" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="44">
   <si>
     <t>簡易地圖</t>
   </si>
@@ -139,10 +139,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>新的地圖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>xxxx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -152,6 +148,22 @@
   </si>
   <si>
     <t>l</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新的地圖往北</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新的地圖往東</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -586,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="5" bestFit="1" customWidth="1"/>
@@ -664,10 +676,21 @@
         <v>36</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -703,6 +726,12 @@
     <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" s="5">
+        <v>6</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1128,10 +1157,10 @@
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>4</v>
@@ -1158,7 +1187,7 @@
         <v>6</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:16">
